--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/10,26/01,10,26 ПОКОМ КИ/дв 01,10,26 мррсч пок ки.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/10,26/01,10,26 ПОКОМ КИ/дв 01,10,26 мррсч пок ки.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\10,26\01,10,26 ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E1D2F4-D245-4EED-A628-43EFE50E0B94}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22C1C2AA-1026-4527-8448-B179BB612CE9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1028,7 +1028,8 @@
     <col min="23" max="24" width="6" customWidth="1"/>
     <col min="25" max="25" width="44.42578125" customWidth="1"/>
     <col min="26" max="26" width="7" customWidth="1"/>
-    <col min="27" max="49" width="3" customWidth="1"/>
+    <col min="27" max="27" width="9.28515625" customWidth="1"/>
+    <col min="28" max="49" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:49" x14ac:dyDescent="0.25">
@@ -1375,7 +1376,10 @@
         <f>SUM(Z6:Z480)</f>
         <v>2670</v>
       </c>
-      <c r="AA5" s="1"/>
+      <c r="AA5" s="4">
+        <f>SUM(AA6:AA480)</f>
+        <v>1201.2524000000001</v>
+      </c>
       <c r="AB5" s="1"/>
       <c r="AC5" s="1"/>
       <c r="AD5" s="1"/>
@@ -1471,7 +1475,10 @@
         <f>ROUND(G6*T6,0)</f>
         <v>0</v>
       </c>
-      <c r="AA6" s="1"/>
+      <c r="AA6" s="1">
+        <f>S6*G6</f>
+        <v>15.604400000000002</v>
+      </c>
       <c r="AB6" s="1"/>
       <c r="AC6" s="1"/>
       <c r="AD6" s="1"/>
@@ -1569,7 +1576,10 @@
         <f t="shared" ref="Z7:Z70" si="5">ROUND(G7*T7,0)</f>
         <v>0</v>
       </c>
-      <c r="AA7" s="1"/>
+      <c r="AA7" s="1">
+        <f t="shared" ref="AA7:AA70" si="6">S7*G7</f>
+        <v>22.6374</v>
+      </c>
       <c r="AB7" s="1"/>
       <c r="AC7" s="1"/>
       <c r="AD7" s="1"/>
@@ -1669,7 +1679,10 @@
         <f t="shared" si="5"/>
         <v>30</v>
       </c>
-      <c r="AA8" s="1"/>
+      <c r="AA8" s="1">
+        <f t="shared" si="6"/>
+        <v>23.381800000000002</v>
+      </c>
       <c r="AB8" s="1"/>
       <c r="AC8" s="1"/>
       <c r="AD8" s="1"/>
@@ -1753,7 +1766,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA9" s="1"/>
+      <c r="AA9" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB9" s="1"/>
       <c r="AC9" s="1"/>
       <c r="AD9" s="1"/>
@@ -1847,7 +1863,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA10" s="1"/>
+      <c r="AA10" s="1">
+        <f t="shared" si="6"/>
+        <v>10.620000000000001</v>
+      </c>
       <c r="AB10" s="1"/>
       <c r="AC10" s="1"/>
       <c r="AD10" s="1"/>
@@ -1924,7 +1943,7 @@
         <v>82.6</v>
       </c>
       <c r="T11" s="5">
-        <f t="shared" ref="T11:T17" si="6">12*S11-R11-Q11-P11-O11-F11</f>
+        <f t="shared" ref="T11:T17" si="7">12*S11-R11-Q11-P11-O11-F11</f>
         <v>342.29294306335203</v>
       </c>
       <c r="U11" s="1">
@@ -1946,7 +1965,10 @@
         <f t="shared" si="5"/>
         <v>154</v>
       </c>
-      <c r="AA11" s="1"/>
+      <c r="AA11" s="1">
+        <f t="shared" si="6"/>
+        <v>37.17</v>
+      </c>
       <c r="AB11" s="1"/>
       <c r="AC11" s="1"/>
       <c r="AD11" s="1"/>
@@ -2042,7 +2064,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA12" s="1"/>
+      <c r="AA12" s="1">
+        <f t="shared" si="6"/>
+        <v>1.02</v>
+      </c>
       <c r="AB12" s="1"/>
       <c r="AC12" s="1"/>
       <c r="AD12" s="1"/>
@@ -2117,7 +2142,7 @@
         <v>5.6</v>
       </c>
       <c r="T13" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>18.5089005235602</v>
       </c>
       <c r="U13" s="1">
@@ -2139,7 +2164,10 @@
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="AA13" s="1"/>
+      <c r="AA13" s="1">
+        <f t="shared" si="6"/>
+        <v>1.68</v>
+      </c>
       <c r="AB13" s="1"/>
       <c r="AC13" s="1"/>
       <c r="AD13" s="1"/>
@@ -2216,7 +2244,7 @@
         <v>20.8</v>
       </c>
       <c r="T14" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>10.600000000000023</v>
       </c>
       <c r="U14" s="1">
@@ -2238,7 +2266,10 @@
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="AA14" s="1"/>
+      <c r="AA14" s="1">
+        <f t="shared" si="6"/>
+        <v>3.5360000000000005</v>
+      </c>
       <c r="AB14" s="1"/>
       <c r="AC14" s="1"/>
       <c r="AD14" s="1"/>
@@ -2334,7 +2365,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA15" s="1"/>
+      <c r="AA15" s="1">
+        <f t="shared" si="6"/>
+        <v>20.296600000000002</v>
+      </c>
       <c r="AB15" s="1"/>
       <c r="AC15" s="1"/>
       <c r="AD15" s="1"/>
@@ -2411,7 +2445,7 @@
         <v>191.55760000000001</v>
       </c>
       <c r="T16" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>348.0912000000003</v>
       </c>
       <c r="U16" s="1">
@@ -2433,7 +2467,10 @@
         <f t="shared" si="5"/>
         <v>348</v>
       </c>
-      <c r="AA16" s="1"/>
+      <c r="AA16" s="1">
+        <f t="shared" si="6"/>
+        <v>191.55760000000001</v>
+      </c>
       <c r="AB16" s="1"/>
       <c r="AC16" s="1"/>
       <c r="AD16" s="1"/>
@@ -2510,7 +2547,7 @@
         <v>15.856399999999999</v>
       </c>
       <c r="T17" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>34.571600000000004</v>
       </c>
       <c r="U17" s="1">
@@ -2532,7 +2569,10 @@
         <f t="shared" si="5"/>
         <v>35</v>
       </c>
-      <c r="AA17" s="1"/>
+      <c r="AA17" s="1">
+        <f t="shared" si="6"/>
+        <v>15.856399999999999</v>
+      </c>
       <c r="AB17" s="1"/>
       <c r="AC17" s="1"/>
       <c r="AD17" s="1"/>
@@ -2618,7 +2658,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA18" s="1"/>
+      <c r="AA18" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB18" s="1"/>
       <c r="AC18" s="1"/>
       <c r="AD18" s="1"/>
@@ -2706,7 +2749,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA19" s="1"/>
+      <c r="AA19" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB19" s="1"/>
       <c r="AC19" s="1"/>
       <c r="AD19" s="1"/>
@@ -2802,7 +2848,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA20" s="1"/>
+      <c r="AA20" s="1">
+        <f t="shared" si="6"/>
+        <v>3.3451999999999997</v>
+      </c>
       <c r="AB20" s="1"/>
       <c r="AC20" s="1"/>
       <c r="AD20" s="1"/>
@@ -2900,7 +2949,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA21" s="1"/>
+      <c r="AA21" s="1">
+        <f t="shared" si="6"/>
+        <v>0.58299999999999996</v>
+      </c>
       <c r="AB21" s="1"/>
       <c r="AC21" s="1"/>
       <c r="AD21" s="1"/>
@@ -2996,7 +3048,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA22" s="1"/>
+      <c r="AA22" s="1">
+        <f t="shared" si="6"/>
+        <v>17.950800000000001</v>
+      </c>
       <c r="AB22" s="1"/>
       <c r="AC22" s="1"/>
       <c r="AD22" s="1"/>
@@ -3084,7 +3139,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA23" s="1"/>
+      <c r="AA23" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB23" s="1"/>
       <c r="AC23" s="1"/>
       <c r="AD23" s="1"/>
@@ -3161,7 +3219,7 @@
         <v>13.150600000000001</v>
       </c>
       <c r="T24" s="5">
-        <f t="shared" ref="T24:T25" si="7">12*S24-R24-Q24-P24-O24-F24</f>
+        <f t="shared" ref="T24:T25" si="8">12*S24-R24-Q24-P24-O24-F24</f>
         <v>51.844200000000029</v>
       </c>
       <c r="U24" s="1">
@@ -3183,7 +3241,10 @@
         <f t="shared" si="5"/>
         <v>52</v>
       </c>
-      <c r="AA24" s="1"/>
+      <c r="AA24" s="1">
+        <f t="shared" si="6"/>
+        <v>13.150600000000001</v>
+      </c>
       <c r="AB24" s="1"/>
       <c r="AC24" s="1"/>
       <c r="AD24" s="1"/>
@@ -3260,7 +3321,7 @@
         <v>23.747800000000002</v>
       </c>
       <c r="T25" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>17.319600000000033</v>
       </c>
       <c r="U25" s="1">
@@ -3284,7 +3345,10 @@
         <f t="shared" si="5"/>
         <v>17</v>
       </c>
-      <c r="AA25" s="1"/>
+      <c r="AA25" s="1">
+        <f t="shared" si="6"/>
+        <v>23.747800000000002</v>
+      </c>
       <c r="AB25" s="1"/>
       <c r="AC25" s="1"/>
       <c r="AD25" s="1"/>
@@ -3382,7 +3446,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA26" s="1"/>
+      <c r="AA26" s="1">
+        <f t="shared" si="6"/>
+        <v>0.97240000000000004</v>
+      </c>
       <c r="AB26" s="1"/>
       <c r="AC26" s="1"/>
       <c r="AD26" s="1"/>
@@ -3482,7 +3549,10 @@
         <f t="shared" si="5"/>
         <v>25</v>
       </c>
-      <c r="AA27" s="1"/>
+      <c r="AA27" s="1">
+        <f t="shared" si="6"/>
+        <v>25.488199999999999</v>
+      </c>
       <c r="AB27" s="1"/>
       <c r="AC27" s="1"/>
       <c r="AD27" s="1"/>
@@ -3566,7 +3636,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA28" s="1"/>
+      <c r="AA28" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB28" s="1"/>
       <c r="AC28" s="1"/>
       <c r="AD28" s="1"/>
@@ -3641,7 +3714,7 @@
         <v>4.5697999999999999</v>
       </c>
       <c r="T29" s="5">
-        <f t="shared" ref="T29:T32" si="8">12*S29-R29-Q29-P29-O29-F29</f>
+        <f t="shared" ref="T29:T32" si="9">12*S29-R29-Q29-P29-O29-F29</f>
         <v>14.713387031064098</v>
       </c>
       <c r="U29" s="1">
@@ -3663,7 +3736,10 @@
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="AA29" s="1"/>
+      <c r="AA29" s="1">
+        <f t="shared" si="6"/>
+        <v>4.5697999999999999</v>
+      </c>
       <c r="AB29" s="1"/>
       <c r="AC29" s="1"/>
       <c r="AD29" s="1"/>
@@ -3749,7 +3825,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA30" s="1"/>
+      <c r="AA30" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB30" s="1"/>
       <c r="AC30" s="1"/>
       <c r="AD30" s="1"/>
@@ -3845,7 +3924,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA31" s="1"/>
+      <c r="AA31" s="1">
+        <f t="shared" si="6"/>
+        <v>10.61</v>
+      </c>
       <c r="AB31" s="1"/>
       <c r="AC31" s="1"/>
       <c r="AD31" s="1"/>
@@ -3922,7 +4004,7 @@
         <v>72.36760000000001</v>
       </c>
       <c r="T32" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>357.00320000000011</v>
       </c>
       <c r="U32" s="1">
@@ -3944,7 +4026,10 @@
         <f t="shared" si="5"/>
         <v>357</v>
       </c>
-      <c r="AA32" s="1"/>
+      <c r="AA32" s="1">
+        <f t="shared" si="6"/>
+        <v>72.36760000000001</v>
+      </c>
       <c r="AB32" s="1"/>
       <c r="AC32" s="1"/>
       <c r="AD32" s="1"/>
@@ -4034,7 +4119,10 @@
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="AA33" s="1"/>
+      <c r="AA33" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB33" s="1"/>
       <c r="AC33" s="1"/>
       <c r="AD33" s="1"/>
@@ -4132,7 +4220,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA34" s="1"/>
+      <c r="AA34" s="1">
+        <f t="shared" si="6"/>
+        <v>0.26960000000000001</v>
+      </c>
       <c r="AB34" s="1"/>
       <c r="AC34" s="1"/>
       <c r="AD34" s="1"/>
@@ -4228,7 +4319,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA35" s="1"/>
+      <c r="AA35" s="1">
+        <f t="shared" si="6"/>
+        <v>2.9064000000000001</v>
+      </c>
       <c r="AB35" s="1"/>
       <c r="AC35" s="1"/>
       <c r="AD35" s="1"/>
@@ -4314,7 +4408,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA36" s="1"/>
+      <c r="AA36" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB36" s="1"/>
       <c r="AC36" s="1"/>
       <c r="AD36" s="1"/>
@@ -4408,7 +4505,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA37" s="1"/>
+      <c r="AA37" s="1">
+        <f t="shared" si="6"/>
+        <v>0.90259999999999996</v>
+      </c>
       <c r="AB37" s="1"/>
       <c r="AC37" s="1"/>
       <c r="AD37" s="1"/>
@@ -4465,7 +4565,7 @@
         <v>567</v>
       </c>
       <c r="L38" s="1">
-        <f t="shared" ref="L38:L69" si="9">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="10">E38-K38</f>
         <v>-434</v>
       </c>
       <c r="M38" s="1"/>
@@ -4481,18 +4581,18 @@
         <v>300</v>
       </c>
       <c r="S38" s="1">
-        <f t="shared" ref="S38:S69" si="10">E38/5</f>
+        <f t="shared" ref="S38:S69" si="11">E38/5</f>
         <v>26.6</v>
       </c>
       <c r="T38" s="5">
         <v>200</v>
       </c>
       <c r="U38" s="1">
-        <f t="shared" ref="U38:U69" si="11">(F38+O38+P38+Q38+R38+T38)/S38</f>
+        <f t="shared" ref="U38:U69" si="12">(F38+O38+P38+Q38+R38+T38)/S38</f>
         <v>38.096396258668847</v>
       </c>
       <c r="V38" s="1">
-        <f t="shared" ref="V38:V69" si="12">(F38+O38+P38+Q38+R38)/S38</f>
+        <f t="shared" ref="V38:V69" si="13">(F38+O38+P38+Q38+R38)/S38</f>
         <v>30.577599266187647</v>
       </c>
       <c r="W38" s="1">
@@ -4506,7 +4606,10 @@
         <f t="shared" si="5"/>
         <v>80</v>
       </c>
-      <c r="AA38" s="1"/>
+      <c r="AA38" s="1">
+        <f t="shared" si="6"/>
+        <v>10.64</v>
+      </c>
       <c r="AB38" s="1"/>
       <c r="AC38" s="1"/>
       <c r="AD38" s="1"/>
@@ -4563,7 +4666,7 @@
         <v>197</v>
       </c>
       <c r="L39" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>14</v>
       </c>
       <c r="M39" s="1"/>
@@ -4579,19 +4682,19 @@
         <v>0</v>
       </c>
       <c r="S39" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>42.2</v>
       </c>
       <c r="T39" s="5">
-        <f t="shared" ref="T39:T66" si="13">12*S39-R39-Q39-P39-O39-F39</f>
+        <f t="shared" ref="T39:T66" si="14">12*S39-R39-Q39-P39-O39-F39</f>
         <v>127.40000000000003</v>
       </c>
       <c r="U39" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>12</v>
       </c>
       <c r="V39" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>8.9810426540284354</v>
       </c>
       <c r="W39" s="1">
@@ -4605,7 +4708,10 @@
         <f t="shared" si="5"/>
         <v>57</v>
       </c>
-      <c r="AA39" s="1"/>
+      <c r="AA39" s="1">
+        <f t="shared" si="6"/>
+        <v>18.990000000000002</v>
+      </c>
       <c r="AB39" s="1"/>
       <c r="AC39" s="1"/>
       <c r="AD39" s="1"/>
@@ -4662,7 +4768,7 @@
         <v>380</v>
       </c>
       <c r="L40" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-227</v>
       </c>
       <c r="M40" s="1"/>
@@ -4678,18 +4784,18 @@
         <v>250</v>
       </c>
       <c r="S40" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>30.6</v>
       </c>
       <c r="T40" s="5">
         <v>150</v>
       </c>
       <c r="U40" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>22.320261437908496</v>
       </c>
       <c r="V40" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>17.41830065359477</v>
       </c>
       <c r="W40" s="1">
@@ -4703,7 +4809,10 @@
         <f t="shared" si="5"/>
         <v>60</v>
       </c>
-      <c r="AA40" s="1"/>
+      <c r="AA40" s="1">
+        <f t="shared" si="6"/>
+        <v>12.240000000000002</v>
+      </c>
       <c r="AB40" s="1"/>
       <c r="AC40" s="1"/>
       <c r="AD40" s="1"/>
@@ -4758,7 +4867,7 @@
         <v>124</v>
       </c>
       <c r="L41" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-52</v>
       </c>
       <c r="M41" s="1"/>
@@ -4774,18 +4883,18 @@
         <v>60</v>
       </c>
       <c r="S41" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>14.4</v>
       </c>
       <c r="T41" s="5">
         <v>50</v>
       </c>
       <c r="U41" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>18.91795865633075</v>
       </c>
       <c r="V41" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>15.445736434108529</v>
       </c>
       <c r="W41" s="1">
@@ -4799,7 +4908,10 @@
         <f t="shared" si="5"/>
         <v>20</v>
       </c>
-      <c r="AA41" s="1"/>
+      <c r="AA41" s="1">
+        <f t="shared" si="6"/>
+        <v>5.7600000000000007</v>
+      </c>
       <c r="AB41" s="1"/>
       <c r="AC41" s="1"/>
       <c r="AD41" s="1"/>
@@ -4856,7 +4968,7 @@
         <v>1.6</v>
       </c>
       <c r="L42" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-0.19600000000000017</v>
       </c>
       <c r="M42" s="1"/>
@@ -4872,18 +4984,18 @@
         <v>0</v>
       </c>
       <c r="S42" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.28079999999999999</v>
       </c>
       <c r="T42" s="5"/>
       <c r="U42" s="1">
-        <f t="shared" si="11"/>
-        <v>184.98389186213572</v>
-      </c>
-      <c r="V42" s="1">
         <f t="shared" si="12"/>
         <v>184.98389186213572</v>
       </c>
+      <c r="V42" s="1">
+        <f t="shared" si="13"/>
+        <v>184.98389186213572</v>
+      </c>
       <c r="W42" s="1">
         <v>0.28079999999999999</v>
       </c>
@@ -4897,7 +5009,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA42" s="1"/>
+      <c r="AA42" s="1">
+        <f t="shared" si="6"/>
+        <v>0.28079999999999999</v>
+      </c>
       <c r="AB42" s="1"/>
       <c r="AC42" s="1"/>
       <c r="AD42" s="1"/>
@@ -4954,7 +5069,7 @@
         <v>32</v>
       </c>
       <c r="L43" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5</v>
       </c>
       <c r="M43" s="1"/>
@@ -4970,18 +5085,18 @@
         <v>0</v>
       </c>
       <c r="S43" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>7.4</v>
       </c>
       <c r="T43" s="5"/>
       <c r="U43" s="1">
-        <f t="shared" si="11"/>
-        <v>49.09779344561953</v>
-      </c>
-      <c r="V43" s="1">
         <f t="shared" si="12"/>
         <v>49.09779344561953</v>
       </c>
+      <c r="V43" s="1">
+        <f t="shared" si="13"/>
+        <v>49.09779344561953</v>
+      </c>
       <c r="W43" s="1">
         <v>3.4</v>
       </c>
@@ -4995,7 +5110,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA43" s="1"/>
+      <c r="AA43" s="1">
+        <f t="shared" si="6"/>
+        <v>0.7400000000000001</v>
+      </c>
       <c r="AB43" s="1"/>
       <c r="AC43" s="1"/>
       <c r="AD43" s="1"/>
@@ -5044,7 +5162,7 @@
         <v>2</v>
       </c>
       <c r="L44" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-2</v>
       </c>
       <c r="M44" s="1"/>
@@ -5060,16 +5178,16 @@
         <v>60</v>
       </c>
       <c r="S44" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="T44" s="5"/>
       <c r="U44" s="1" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V44" s="1" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W44" s="1">
@@ -5083,7 +5201,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA44" s="1"/>
+      <c r="AA44" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB44" s="1"/>
       <c r="AC44" s="1"/>
       <c r="AD44" s="1"/>
@@ -5138,7 +5259,7 @@
         <v>40</v>
       </c>
       <c r="L45" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-10.478999999999999</v>
       </c>
       <c r="M45" s="1"/>
@@ -5154,18 +5275,18 @@
         <v>0</v>
       </c>
       <c r="S45" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.9042000000000003</v>
       </c>
       <c r="T45" s="5">
         <v>10</v>
       </c>
       <c r="U45" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>16.127647335105895</v>
       </c>
       <c r="V45" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>14.433937772421704</v>
       </c>
       <c r="W45" s="1">
@@ -5181,7 +5302,10 @@
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="AA45" s="1"/>
+      <c r="AA45" s="1">
+        <f t="shared" si="6"/>
+        <v>5.9042000000000003</v>
+      </c>
       <c r="AB45" s="1"/>
       <c r="AC45" s="1"/>
       <c r="AD45" s="1"/>
@@ -5236,7 +5360,7 @@
         <v>114</v>
       </c>
       <c r="L46" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-109</v>
       </c>
       <c r="M46" s="1"/>
@@ -5252,16 +5376,16 @@
         <v>150</v>
       </c>
       <c r="S46" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="T46" s="5"/>
       <c r="U46" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>411.70383275261327</v>
       </c>
       <c r="V46" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>411.70383275261327</v>
       </c>
       <c r="W46" s="1">
@@ -5275,7 +5399,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA46" s="1"/>
+      <c r="AA46" s="1">
+        <f t="shared" si="6"/>
+        <v>0.4</v>
+      </c>
       <c r="AB46" s="1"/>
       <c r="AC46" s="1"/>
       <c r="AD46" s="1"/>
@@ -5332,7 +5459,7 @@
         <v>104</v>
       </c>
       <c r="L47" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-90</v>
       </c>
       <c r="M47" s="1"/>
@@ -5348,16 +5475,16 @@
         <v>0</v>
       </c>
       <c r="S47" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.8</v>
       </c>
       <c r="T47" s="5"/>
       <c r="U47" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>70.889212827988359</v>
       </c>
       <c r="V47" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>70.889212827988359</v>
       </c>
       <c r="W47" s="1">
@@ -5371,7 +5498,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA47" s="1"/>
+      <c r="AA47" s="1">
+        <f t="shared" si="6"/>
+        <v>1.1199999999999999</v>
+      </c>
       <c r="AB47" s="1"/>
       <c r="AC47" s="1"/>
       <c r="AD47" s="1"/>
@@ -5426,7 +5556,7 @@
         <v>80</v>
       </c>
       <c r="L48" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-11.816999999999993</v>
       </c>
       <c r="M48" s="1"/>
@@ -5442,19 +5572,19 @@
         <v>20</v>
       </c>
       <c r="S48" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>13.636600000000001</v>
       </c>
       <c r="T48" s="5">
+        <f t="shared" si="14"/>
+        <v>52.641200000000012</v>
+      </c>
+      <c r="U48" s="1">
+        <f t="shared" si="12"/>
+        <v>12</v>
+      </c>
+      <c r="V48" s="1">
         <f t="shared" si="13"/>
-        <v>52.641200000000012</v>
-      </c>
-      <c r="U48" s="1">
-        <f t="shared" si="11"/>
-        <v>12</v>
-      </c>
-      <c r="V48" s="1">
-        <f t="shared" si="12"/>
         <v>8.1397122449877539</v>
       </c>
       <c r="W48" s="1">
@@ -5470,7 +5600,10 @@
         <f t="shared" si="5"/>
         <v>53</v>
       </c>
-      <c r="AA48" s="1"/>
+      <c r="AA48" s="1">
+        <f t="shared" si="6"/>
+        <v>13.636600000000001</v>
+      </c>
       <c r="AB48" s="1"/>
       <c r="AC48" s="1"/>
       <c r="AD48" s="1"/>
@@ -5519,7 +5652,7 @@
         <v>37</v>
       </c>
       <c r="L49" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-37</v>
       </c>
       <c r="M49" s="1"/>
@@ -5537,16 +5670,16 @@
         <v>250</v>
       </c>
       <c r="S49" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="T49" s="5"/>
       <c r="U49" s="1" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V49" s="1" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W49" s="1">
@@ -5560,7 +5693,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA49" s="1"/>
+      <c r="AA49" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB49" s="1"/>
       <c r="AC49" s="1"/>
       <c r="AD49" s="1"/>
@@ -5617,7 +5753,7 @@
         <v>215</v>
       </c>
       <c r="L50" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-3</v>
       </c>
       <c r="M50" s="1"/>
@@ -5633,19 +5769,19 @@
         <v>141.19999999999999</v>
       </c>
       <c r="S50" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>42.4</v>
       </c>
       <c r="T50" s="5">
+        <f t="shared" si="14"/>
+        <v>201.59999999999997</v>
+      </c>
+      <c r="U50" s="1">
+        <f t="shared" si="12"/>
+        <v>12</v>
+      </c>
+      <c r="V50" s="1">
         <f t="shared" si="13"/>
-        <v>201.59999999999997</v>
-      </c>
-      <c r="U50" s="1">
-        <f t="shared" si="11"/>
-        <v>12</v>
-      </c>
-      <c r="V50" s="1">
-        <f t="shared" si="12"/>
         <v>7.2452830188679247</v>
       </c>
       <c r="W50" s="1">
@@ -5659,7 +5795,10 @@
         <f t="shared" si="5"/>
         <v>81</v>
       </c>
-      <c r="AA50" s="1"/>
+      <c r="AA50" s="1">
+        <f t="shared" si="6"/>
+        <v>16.96</v>
+      </c>
       <c r="AB50" s="1"/>
       <c r="AC50" s="1"/>
       <c r="AD50" s="1"/>
@@ -5714,7 +5853,7 @@
         <v>45.1</v>
       </c>
       <c r="L51" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-43.734999999999999</v>
       </c>
       <c r="M51" s="1"/>
@@ -5730,16 +5869,16 @@
         <v>0</v>
       </c>
       <c r="S51" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.27300000000000002</v>
       </c>
       <c r="T51" s="5"/>
       <c r="U51" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>519.84102564102545</v>
       </c>
       <c r="V51" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>519.84102564102545</v>
       </c>
       <c r="W51" s="1">
@@ -5753,7 +5892,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA51" s="1"/>
+      <c r="AA51" s="1">
+        <f t="shared" si="6"/>
+        <v>0.27300000000000002</v>
+      </c>
       <c r="AB51" s="1"/>
       <c r="AC51" s="1"/>
       <c r="AD51" s="1"/>
@@ -5810,7 +5952,7 @@
         <v>131.1</v>
       </c>
       <c r="L52" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-39.091999999999999</v>
       </c>
       <c r="M52" s="1"/>
@@ -5826,19 +5968,19 @@
         <v>54.752200000000023</v>
       </c>
       <c r="S52" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>18.401599999999998</v>
       </c>
       <c r="T52" s="5">
+        <f t="shared" si="14"/>
+        <v>112.13199999999995</v>
+      </c>
+      <c r="U52" s="1">
+        <f t="shared" si="12"/>
+        <v>12</v>
+      </c>
+      <c r="V52" s="1">
         <f t="shared" si="13"/>
-        <v>112.13199999999995</v>
-      </c>
-      <c r="U52" s="1">
-        <f t="shared" si="11"/>
-        <v>12</v>
-      </c>
-      <c r="V52" s="1">
-        <f t="shared" si="12"/>
         <v>5.9063994435266514</v>
       </c>
       <c r="W52" s="1">
@@ -5854,7 +5996,10 @@
         <f t="shared" si="5"/>
         <v>112</v>
       </c>
-      <c r="AA52" s="1"/>
+      <c r="AA52" s="1">
+        <f t="shared" si="6"/>
+        <v>18.401599999999998</v>
+      </c>
       <c r="AB52" s="1"/>
       <c r="AC52" s="1"/>
       <c r="AD52" s="1"/>
@@ -5909,7 +6054,7 @@
         <v>11.7</v>
       </c>
       <c r="L53" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.109</v>
       </c>
       <c r="M53" s="1"/>
@@ -5925,16 +6070,16 @@
         <v>0</v>
       </c>
       <c r="S53" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.7618</v>
       </c>
       <c r="T53" s="5"/>
       <c r="U53" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>50.276269099862411</v>
       </c>
       <c r="V53" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>50.276269099862411</v>
       </c>
       <c r="W53" s="1">
@@ -5948,7 +6093,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA53" s="1"/>
+      <c r="AA53" s="1">
+        <f t="shared" si="6"/>
+        <v>2.7618</v>
+      </c>
       <c r="AB53" s="1"/>
       <c r="AC53" s="1"/>
       <c r="AD53" s="1"/>
@@ -6005,7 +6153,7 @@
         <v>85</v>
       </c>
       <c r="L54" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-5</v>
       </c>
       <c r="M54" s="1"/>
@@ -6021,16 +6169,16 @@
         <v>0</v>
       </c>
       <c r="S54" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>16</v>
       </c>
       <c r="T54" s="5"/>
       <c r="U54" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>12.9375</v>
       </c>
       <c r="V54" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>12.9375</v>
       </c>
       <c r="W54" s="1">
@@ -6044,7 +6192,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA54" s="1"/>
+      <c r="AA54" s="1">
+        <f t="shared" si="6"/>
+        <v>7.2</v>
+      </c>
       <c r="AB54" s="1"/>
       <c r="AC54" s="1"/>
       <c r="AD54" s="1"/>
@@ -6101,7 +6252,7 @@
         <v>150</v>
       </c>
       <c r="L55" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-20</v>
       </c>
       <c r="M55" s="1"/>
@@ -6117,19 +6268,19 @@
         <v>47.111627906976743</v>
       </c>
       <c r="S55" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>26</v>
       </c>
       <c r="T55" s="5">
+        <f t="shared" si="14"/>
+        <v>81.19999999999996</v>
+      </c>
+      <c r="U55" s="1">
+        <f t="shared" si="12"/>
+        <v>12</v>
+      </c>
+      <c r="V55" s="1">
         <f t="shared" si="13"/>
-        <v>81.19999999999996</v>
-      </c>
-      <c r="U55" s="1">
-        <f t="shared" si="11"/>
-        <v>12</v>
-      </c>
-      <c r="V55" s="1">
-        <f t="shared" si="12"/>
         <v>8.8769230769230774</v>
       </c>
       <c r="W55" s="1">
@@ -6143,7 +6294,10 @@
         <f t="shared" si="5"/>
         <v>37</v>
       </c>
-      <c r="AA55" s="1"/>
+      <c r="AA55" s="1">
+        <f t="shared" si="6"/>
+        <v>11.700000000000001</v>
+      </c>
       <c r="AB55" s="1"/>
       <c r="AC55" s="1"/>
       <c r="AD55" s="1"/>
@@ -6192,7 +6346,7 @@
         <v>6</v>
       </c>
       <c r="L56" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-6</v>
       </c>
       <c r="M56" s="1"/>
@@ -6208,16 +6362,16 @@
         <v>5</v>
       </c>
       <c r="S56" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="T56" s="5"/>
       <c r="U56" s="1" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V56" s="1" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W56" s="1">
@@ -6231,7 +6385,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA56" s="1"/>
+      <c r="AA56" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB56" s="1"/>
       <c r="AC56" s="1"/>
       <c r="AD56" s="1"/>
@@ -6280,7 +6437,7 @@
         <v>8</v>
       </c>
       <c r="L57" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-8</v>
       </c>
       <c r="M57" s="1"/>
@@ -6296,16 +6453,16 @@
         <v>5</v>
       </c>
       <c r="S57" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="T57" s="5"/>
       <c r="U57" s="1" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V57" s="1" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W57" s="1">
@@ -6319,7 +6476,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA57" s="1"/>
+      <c r="AA57" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB57" s="1"/>
       <c r="AC57" s="1"/>
       <c r="AD57" s="1"/>
@@ -6376,7 +6536,7 @@
         <v>77.7</v>
       </c>
       <c r="L58" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-30.129000000000005</v>
       </c>
       <c r="M58" s="1"/>
@@ -6392,18 +6552,18 @@
         <v>0</v>
       </c>
       <c r="S58" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>9.5141999999999989</v>
       </c>
       <c r="T58" s="5">
         <v>10</v>
       </c>
       <c r="U58" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>12.530848626263902</v>
       </c>
       <c r="V58" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>11.479788106199157</v>
       </c>
       <c r="W58" s="1">
@@ -6419,7 +6579,10 @@
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="AA58" s="1"/>
+      <c r="AA58" s="1">
+        <f t="shared" si="6"/>
+        <v>9.5141999999999989</v>
+      </c>
       <c r="AB58" s="1"/>
       <c r="AC58" s="1"/>
       <c r="AD58" s="1"/>
@@ -6478,7 +6641,7 @@
         <v>39</v>
       </c>
       <c r="L59" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>22</v>
       </c>
       <c r="M59" s="1"/>
@@ -6494,18 +6657,18 @@
         <v>0</v>
       </c>
       <c r="S59" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>12.2</v>
       </c>
       <c r="T59" s="5"/>
       <c r="U59" s="1">
-        <f t="shared" si="11"/>
-        <v>12.793028472821398</v>
-      </c>
-      <c r="V59" s="1">
         <f t="shared" si="12"/>
         <v>12.793028472821398</v>
       </c>
+      <c r="V59" s="1">
+        <f t="shared" si="13"/>
+        <v>12.793028472821398</v>
+      </c>
       <c r="W59" s="1">
         <v>6.2</v>
       </c>
@@ -6519,7 +6682,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA59" s="1"/>
+      <c r="AA59" s="1">
+        <f t="shared" si="6"/>
+        <v>1.22</v>
+      </c>
       <c r="AB59" s="1"/>
       <c r="AC59" s="1"/>
       <c r="AD59" s="1"/>
@@ -6576,7 +6742,7 @@
         <v>138.9</v>
       </c>
       <c r="L60" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-79.722000000000008</v>
       </c>
       <c r="M60" s="1"/>
@@ -6592,18 +6758,18 @@
         <v>0</v>
       </c>
       <c r="S60" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>11.835599999999999</v>
       </c>
       <c r="T60" s="5"/>
       <c r="U60" s="1">
-        <f t="shared" si="11"/>
-        <v>15.342580828696564</v>
-      </c>
-      <c r="V60" s="1">
         <f t="shared" si="12"/>
         <v>15.342580828696564</v>
       </c>
+      <c r="V60" s="1">
+        <f t="shared" si="13"/>
+        <v>15.342580828696564</v>
+      </c>
       <c r="W60" s="1">
         <v>11.785399999999999</v>
       </c>
@@ -6617,7 +6783,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA60" s="1"/>
+      <c r="AA60" s="1">
+        <f t="shared" si="6"/>
+        <v>11.835599999999999</v>
+      </c>
       <c r="AB60" s="1"/>
       <c r="AC60" s="1"/>
       <c r="AD60" s="1"/>
@@ -6666,7 +6835,7 @@
         <v>9</v>
       </c>
       <c r="L61" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-9</v>
       </c>
       <c r="M61" s="1"/>
@@ -6682,16 +6851,16 @@
         <v>10</v>
       </c>
       <c r="S61" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="T61" s="5"/>
       <c r="U61" s="1" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V61" s="1" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W61" s="1">
@@ -6705,7 +6874,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA61" s="1"/>
+      <c r="AA61" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB61" s="1"/>
       <c r="AC61" s="1"/>
       <c r="AD61" s="1"/>
@@ -6762,7 +6934,7 @@
         <v>28</v>
       </c>
       <c r="L62" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5</v>
       </c>
       <c r="M62" s="1"/>
@@ -6778,18 +6950,18 @@
         <v>0</v>
       </c>
       <c r="S62" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>6.6</v>
       </c>
       <c r="T62" s="5"/>
       <c r="U62" s="1">
-        <f t="shared" si="11"/>
-        <v>30.959397511460384</v>
-      </c>
-      <c r="V62" s="1">
         <f t="shared" si="12"/>
         <v>30.959397511460384</v>
       </c>
+      <c r="V62" s="1">
+        <f t="shared" si="13"/>
+        <v>30.959397511460384</v>
+      </c>
       <c r="W62" s="1">
         <v>3.8</v>
       </c>
@@ -6803,7 +6975,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA62" s="1"/>
+      <c r="AA62" s="1">
+        <f t="shared" si="6"/>
+        <v>0.66</v>
+      </c>
       <c r="AB62" s="1"/>
       <c r="AC62" s="1"/>
       <c r="AD62" s="1"/>
@@ -6858,7 +7033,7 @@
         <v>11</v>
       </c>
       <c r="L63" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-6</v>
       </c>
       <c r="M63" s="1"/>
@@ -6874,18 +7049,18 @@
         <v>0</v>
       </c>
       <c r="S63" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="T63" s="5">
         <v>6</v>
       </c>
       <c r="U63" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>18</v>
       </c>
       <c r="V63" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>12</v>
       </c>
       <c r="W63" s="1">
@@ -6899,7 +7074,10 @@
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="AA63" s="1"/>
+      <c r="AA63" s="1">
+        <f t="shared" si="6"/>
+        <v>0.4</v>
+      </c>
       <c r="AB63" s="1"/>
       <c r="AC63" s="1"/>
       <c r="AD63" s="1"/>
@@ -6954,7 +7132,7 @@
         <v>53</v>
       </c>
       <c r="L64" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-53</v>
       </c>
       <c r="M64" s="1"/>
@@ -6970,16 +7148,16 @@
         <v>50</v>
       </c>
       <c r="S64" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="T64" s="5"/>
       <c r="U64" s="1" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V64" s="1" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W64" s="1">
@@ -6993,7 +7171,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA64" s="1"/>
+      <c r="AA64" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB64" s="1"/>
       <c r="AC64" s="1"/>
       <c r="AD64" s="1"/>
@@ -7042,7 +7223,7 @@
         <v>2.6</v>
       </c>
       <c r="L65" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-2.6</v>
       </c>
       <c r="M65" s="1"/>
@@ -7058,16 +7239,16 @@
         <v>50</v>
       </c>
       <c r="S65" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="T65" s="5"/>
       <c r="U65" s="1" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V65" s="1" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W65" s="1">
@@ -7081,7 +7262,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA65" s="1"/>
+      <c r="AA65" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB65" s="1"/>
       <c r="AC65" s="1"/>
       <c r="AD65" s="1"/>
@@ -7138,7 +7322,7 @@
         <v>232</v>
       </c>
       <c r="L66" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-60</v>
       </c>
       <c r="M66" s="1"/>
@@ -7154,19 +7338,19 @@
         <v>0</v>
       </c>
       <c r="S66" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>34.4</v>
       </c>
       <c r="T66" s="5">
+        <f t="shared" si="14"/>
+        <v>115.06491994177577</v>
+      </c>
+      <c r="U66" s="1">
+        <f t="shared" si="12"/>
+        <v>12</v>
+      </c>
+      <c r="V66" s="1">
         <f t="shared" si="13"/>
-        <v>115.06491994177577</v>
-      </c>
-      <c r="U66" s="1">
-        <f t="shared" si="11"/>
-        <v>12</v>
-      </c>
-      <c r="V66" s="1">
-        <f t="shared" si="12"/>
         <v>8.6550895365762841</v>
       </c>
       <c r="W66" s="1">
@@ -7180,7 +7364,10 @@
         <f t="shared" si="5"/>
         <v>46</v>
       </c>
-      <c r="AA66" s="1"/>
+      <c r="AA66" s="1">
+        <f t="shared" si="6"/>
+        <v>13.76</v>
+      </c>
       <c r="AB66" s="1"/>
       <c r="AC66" s="1"/>
       <c r="AD66" s="1"/>
@@ -7231,7 +7418,7 @@
         <v>38</v>
       </c>
       <c r="L67" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-38</v>
       </c>
       <c r="M67" s="1"/>
@@ -7247,16 +7434,16 @@
         <v>100</v>
       </c>
       <c r="S67" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="T67" s="5"/>
       <c r="U67" s="1" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V67" s="1" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W67" s="1">
@@ -7270,7 +7457,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA67" s="1"/>
+      <c r="AA67" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB67" s="1"/>
       <c r="AC67" s="1"/>
       <c r="AD67" s="1"/>
@@ -7327,7 +7517,7 @@
         <v>81.3</v>
       </c>
       <c r="L68" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-6.2289999999999992</v>
       </c>
       <c r="M68" s="1"/>
@@ -7345,18 +7535,18 @@
         <v>0</v>
       </c>
       <c r="S68" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>15.014199999999999</v>
       </c>
       <c r="T68" s="5">
         <v>100</v>
       </c>
       <c r="U68" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>7.7066712920154314</v>
       </c>
       <c r="V68" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.0463097675918858</v>
       </c>
       <c r="W68" s="1">
@@ -7370,7 +7560,10 @@
         <f t="shared" si="5"/>
         <v>100</v>
       </c>
-      <c r="AA68" s="1"/>
+      <c r="AA68" s="1">
+        <f t="shared" si="6"/>
+        <v>15.014199999999999</v>
+      </c>
       <c r="AB68" s="1"/>
       <c r="AC68" s="1"/>
       <c r="AD68" s="1"/>
@@ -7425,7 +7618,7 @@
         <v>75.599999999999994</v>
       </c>
       <c r="L69" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-0.18099999999999739</v>
       </c>
       <c r="M69" s="1"/>
@@ -7443,18 +7636,18 @@
         <v>0</v>
       </c>
       <c r="S69" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>15.0838</v>
       </c>
       <c r="T69" s="5">
         <v>100</v>
       </c>
       <c r="U69" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>7.2327418398729542</v>
       </c>
       <c r="V69" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.6031127013269646</v>
       </c>
       <c r="W69" s="1">
@@ -7468,7 +7661,10 @@
         <f t="shared" si="5"/>
         <v>100</v>
       </c>
-      <c r="AA69" s="1"/>
+      <c r="AA69" s="1">
+        <f t="shared" si="6"/>
+        <v>15.0838</v>
+      </c>
       <c r="AB69" s="1"/>
       <c r="AC69" s="1"/>
       <c r="AD69" s="1"/>
@@ -7525,7 +7721,7 @@
         <v>34.200000000000003</v>
       </c>
       <c r="L70" s="1">
-        <f t="shared" ref="L70:L101" si="14">E70-K70</f>
+        <f t="shared" ref="L70:L101" si="15">E70-K70</f>
         <v>-13.232000000000003</v>
       </c>
       <c r="M70" s="1"/>
@@ -7543,18 +7739,18 @@
         <v>0</v>
       </c>
       <c r="S70" s="1">
-        <f t="shared" ref="S70:S101" si="15">E70/5</f>
+        <f t="shared" ref="S70:S101" si="16">E70/5</f>
         <v>4.1936</v>
       </c>
       <c r="T70" s="5">
         <v>50</v>
       </c>
       <c r="U70" s="1">
-        <f t="shared" ref="U70:U101" si="16">(F70+O70+P70+Q70+R70+T70)/S70</f>
+        <f t="shared" ref="U70:U101" si="17">(F70+O70+P70+Q70+R70+T70)/S70</f>
         <v>52.411647238024692</v>
       </c>
       <c r="V70" s="1">
-        <f t="shared" ref="V70:V101" si="17">(F70+O70+P70+Q70+R70)/S70</f>
+        <f t="shared" ref="V70:V101" si="18">(F70+O70+P70+Q70+R70)/S70</f>
         <v>40.48871705870382</v>
       </c>
       <c r="W70" s="1">
@@ -7568,7 +7764,10 @@
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="AA70" s="1"/>
+      <c r="AA70" s="1">
+        <f t="shared" si="6"/>
+        <v>4.1936</v>
+      </c>
       <c r="AB70" s="1"/>
       <c r="AC70" s="1"/>
       <c r="AD70" s="1"/>
@@ -7617,7 +7816,7 @@
         <v>7.9</v>
       </c>
       <c r="L71" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-7.9</v>
       </c>
       <c r="M71" s="1"/>
@@ -7633,18 +7832,18 @@
         <v>0</v>
       </c>
       <c r="S71" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="T71" s="5"/>
       <c r="U71" s="1" t="e">
-        <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V71" s="1" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="V71" s="1" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="W71" s="1">
         <v>0</v>
       </c>
@@ -7653,10 +7852,13 @@
       </c>
       <c r="Y71" s="1"/>
       <c r="Z71" s="1">
-        <f t="shared" ref="Z71:Z131" si="18">ROUND(G71*T71,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AA71" s="1"/>
+        <f t="shared" ref="Z71:Z131" si="19">ROUND(G71*T71,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA71" s="1">
+        <f t="shared" ref="AA71:AA131" si="20">S71*G71</f>
+        <v>0</v>
+      </c>
       <c r="AB71" s="1"/>
       <c r="AC71" s="1"/>
       <c r="AD71" s="1"/>
@@ -7701,7 +7903,7 @@
       <c r="J72" s="10"/>
       <c r="K72" s="10"/>
       <c r="L72" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M72" s="10"/>
@@ -7715,18 +7917,18 @@
         <v>0</v>
       </c>
       <c r="S72" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="T72" s="12"/>
       <c r="U72" s="10" t="e">
-        <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V72" s="10" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="V72" s="10" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="W72" s="10">
         <v>0</v>
       </c>
@@ -7737,10 +7939,13 @@
         <v>34</v>
       </c>
       <c r="Z72" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA72" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA72" s="1">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
       <c r="AB72" s="1"/>
       <c r="AC72" s="1"/>
       <c r="AD72" s="1"/>
@@ -7793,7 +7998,7 @@
         <v>9.3000000000000007</v>
       </c>
       <c r="L73" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-9.3000000000000007</v>
       </c>
       <c r="M73" s="1"/>
@@ -7809,18 +8014,18 @@
         <v>120</v>
       </c>
       <c r="S73" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="T73" s="5"/>
       <c r="U73" s="1" t="e">
-        <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V73" s="1" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="V73" s="1" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="W73" s="1">
         <v>0</v>
       </c>
@@ -7829,10 +8034,13 @@
       </c>
       <c r="Y73" s="1"/>
       <c r="Z73" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA73" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA73" s="1">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
       <c r="AB73" s="1"/>
       <c r="AC73" s="1"/>
       <c r="AD73" s="1"/>
@@ -7889,7 +8097,7 @@
         <v>44</v>
       </c>
       <c r="L74" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-26</v>
       </c>
       <c r="M74" s="1"/>
@@ -7905,18 +8113,18 @@
         <v>0</v>
       </c>
       <c r="S74" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>3.6</v>
       </c>
       <c r="T74" s="5"/>
       <c r="U74" s="1">
-        <f t="shared" si="16"/>
-        <v>88.028368794326241</v>
-      </c>
-      <c r="V74" s="1">
         <f t="shared" si="17"/>
         <v>88.028368794326241</v>
       </c>
+      <c r="V74" s="1">
+        <f t="shared" si="18"/>
+        <v>88.028368794326241</v>
+      </c>
       <c r="W74" s="1">
         <v>5.9474</v>
       </c>
@@ -7927,10 +8135,13 @@
         <v>50</v>
       </c>
       <c r="Z74" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA74" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA74" s="1">
+        <f t="shared" si="20"/>
+        <v>2.16</v>
+      </c>
       <c r="AB74" s="1"/>
       <c r="AC74" s="1"/>
       <c r="AD74" s="1"/>
@@ -7987,7 +8198,7 @@
         <v>63</v>
       </c>
       <c r="L75" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-45</v>
       </c>
       <c r="M75" s="1"/>
@@ -8003,18 +8214,18 @@
         <v>0</v>
       </c>
       <c r="S75" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>3.6</v>
       </c>
       <c r="T75" s="5"/>
       <c r="U75" s="1">
-        <f t="shared" si="16"/>
-        <v>74.795281582952825</v>
-      </c>
-      <c r="V75" s="1">
         <f t="shared" si="17"/>
         <v>74.795281582952825</v>
       </c>
+      <c r="V75" s="1">
+        <f t="shared" si="18"/>
+        <v>74.795281582952825</v>
+      </c>
       <c r="W75" s="1">
         <v>9.4</v>
       </c>
@@ -8025,10 +8236,13 @@
         <v>50</v>
       </c>
       <c r="Z75" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA75" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA75" s="1">
+        <f t="shared" si="20"/>
+        <v>2.16</v>
+      </c>
       <c r="AB75" s="1"/>
       <c r="AC75" s="1"/>
       <c r="AD75" s="1"/>
@@ -8083,7 +8297,7 @@
         <v>32</v>
       </c>
       <c r="L76" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-1</v>
       </c>
       <c r="M76" s="1"/>
@@ -8099,18 +8313,18 @@
         <v>0</v>
       </c>
       <c r="S76" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>6.2</v>
       </c>
       <c r="T76" s="5"/>
       <c r="U76" s="1">
-        <f t="shared" si="16"/>
-        <v>22.706744868035191</v>
-      </c>
-      <c r="V76" s="1">
         <f t="shared" si="17"/>
         <v>22.706744868035191</v>
       </c>
+      <c r="V76" s="1">
+        <f t="shared" si="18"/>
+        <v>22.706744868035191</v>
+      </c>
       <c r="W76" s="1">
         <v>1.8</v>
       </c>
@@ -8119,10 +8333,13 @@
       </c>
       <c r="Y76" s="1"/>
       <c r="Z76" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA76" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA76" s="1">
+        <f t="shared" si="20"/>
+        <v>2.4800000000000004</v>
+      </c>
       <c r="AB76" s="1"/>
       <c r="AC76" s="1"/>
       <c r="AD76" s="1"/>
@@ -8179,7 +8396,7 @@
         <v>48</v>
       </c>
       <c r="L77" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2</v>
       </c>
       <c r="M77" s="1"/>
@@ -8195,18 +8412,18 @@
         <v>0</v>
       </c>
       <c r="S77" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>10</v>
       </c>
       <c r="T77" s="5"/>
       <c r="U77" s="1">
-        <f t="shared" si="16"/>
-        <v>18.541632653061225</v>
-      </c>
-      <c r="V77" s="1">
         <f t="shared" si="17"/>
         <v>18.541632653061225</v>
       </c>
+      <c r="V77" s="1">
+        <f t="shared" si="18"/>
+        <v>18.541632653061225</v>
+      </c>
       <c r="W77" s="1">
         <v>9.4</v>
       </c>
@@ -8215,10 +8432,13 @@
       </c>
       <c r="Y77" s="1"/>
       <c r="Z77" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA77" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA77" s="1">
+        <f t="shared" si="20"/>
+        <v>3.3000000000000003</v>
+      </c>
       <c r="AB77" s="1"/>
       <c r="AC77" s="1"/>
       <c r="AD77" s="1"/>
@@ -8273,7 +8493,7 @@
         <v>55</v>
       </c>
       <c r="L78" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-9</v>
       </c>
       <c r="M78" s="1"/>
@@ -8289,18 +8509,18 @@
         <v>0</v>
       </c>
       <c r="S78" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>9.1999999999999993</v>
       </c>
       <c r="T78" s="5"/>
       <c r="U78" s="1">
-        <f t="shared" si="16"/>
-        <v>23.786145204909509</v>
-      </c>
-      <c r="V78" s="1">
         <f t="shared" si="17"/>
         <v>23.786145204909509</v>
       </c>
+      <c r="V78" s="1">
+        <f t="shared" si="18"/>
+        <v>23.786145204909509</v>
+      </c>
       <c r="W78" s="1">
         <v>2</v>
       </c>
@@ -8309,10 +8529,13 @@
       </c>
       <c r="Y78" s="1"/>
       <c r="Z78" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA78" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA78" s="1">
+        <f t="shared" si="20"/>
+        <v>3.2199999999999998</v>
+      </c>
       <c r="AB78" s="1"/>
       <c r="AC78" s="1"/>
       <c r="AD78" s="1"/>
@@ -8365,7 +8588,7 @@
         <v>13</v>
       </c>
       <c r="L79" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-12</v>
       </c>
       <c r="M79" s="1"/>
@@ -8381,18 +8604,18 @@
         <v>0</v>
       </c>
       <c r="S79" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.2</v>
       </c>
       <c r="T79" s="5"/>
       <c r="U79" s="1">
-        <f t="shared" si="16"/>
-        <v>145</v>
-      </c>
-      <c r="V79" s="1">
         <f t="shared" si="17"/>
         <v>145</v>
       </c>
+      <c r="V79" s="1">
+        <f t="shared" si="18"/>
+        <v>145</v>
+      </c>
       <c r="W79" s="1">
         <v>0.4</v>
       </c>
@@ -8401,10 +8624,13 @@
       </c>
       <c r="Y79" s="1"/>
       <c r="Z79" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA79" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA79" s="1">
+        <f t="shared" si="20"/>
+        <v>7.3999999999999996E-2</v>
+      </c>
       <c r="AB79" s="1"/>
       <c r="AC79" s="1"/>
       <c r="AD79" s="1"/>
@@ -8461,7 +8687,7 @@
         <v>69</v>
       </c>
       <c r="L80" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-48</v>
       </c>
       <c r="M80" s="1"/>
@@ -8477,18 +8703,18 @@
         <v>0</v>
       </c>
       <c r="S80" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>4.2</v>
       </c>
       <c r="T80" s="5"/>
       <c r="U80" s="1">
-        <f t="shared" si="16"/>
-        <v>59.166199813258636</v>
-      </c>
-      <c r="V80" s="1">
         <f t="shared" si="17"/>
         <v>59.166199813258636</v>
       </c>
+      <c r="V80" s="1">
+        <f t="shared" si="18"/>
+        <v>59.166199813258636</v>
+      </c>
       <c r="W80" s="1">
         <v>7</v>
       </c>
@@ -8499,10 +8725,13 @@
         <v>50</v>
       </c>
       <c r="Z80" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA80" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA80" s="1">
+        <f t="shared" si="20"/>
+        <v>2.52</v>
+      </c>
       <c r="AB80" s="1"/>
       <c r="AC80" s="1"/>
       <c r="AD80" s="1"/>
@@ -8557,7 +8786,7 @@
         <v>30</v>
       </c>
       <c r="L81" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-12</v>
       </c>
       <c r="M81" s="1"/>
@@ -8573,19 +8802,19 @@
         <v>0</v>
       </c>
       <c r="S81" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>3.6</v>
       </c>
       <c r="T81" s="5">
-        <f t="shared" ref="T81" si="19">12*S81-R81-Q81-P81-O81-F81</f>
+        <f t="shared" ref="T81" si="21">12*S81-R81-Q81-P81-O81-F81</f>
         <v>10.981659388646293</v>
       </c>
       <c r="U81" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>12</v>
       </c>
       <c r="V81" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>8.9495390587093642</v>
       </c>
       <c r="W81" s="1">
@@ -8596,10 +8825,13 @@
       </c>
       <c r="Y81" s="1"/>
       <c r="Z81" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>4</v>
       </c>
-      <c r="AA81" s="1"/>
+      <c r="AA81" s="1">
+        <f t="shared" si="20"/>
+        <v>1.1880000000000002</v>
+      </c>
       <c r="AB81" s="1"/>
       <c r="AC81" s="1"/>
       <c r="AD81" s="1"/>
@@ -8656,7 +8888,7 @@
         <v>13</v>
       </c>
       <c r="L82" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-3</v>
       </c>
       <c r="M82" s="1"/>
@@ -8672,18 +8904,18 @@
         <v>0</v>
       </c>
       <c r="S82" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2</v>
       </c>
       <c r="T82" s="5"/>
       <c r="U82" s="1">
-        <f t="shared" si="16"/>
-        <v>21.5</v>
-      </c>
-      <c r="V82" s="1">
         <f t="shared" si="17"/>
         <v>21.5</v>
       </c>
+      <c r="V82" s="1">
+        <f t="shared" si="18"/>
+        <v>21.5</v>
+      </c>
       <c r="W82" s="1">
         <v>2.2000000000000002</v>
       </c>
@@ -8694,10 +8926,13 @@
         <v>61</v>
       </c>
       <c r="Z82" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA82" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA82" s="1">
+        <f t="shared" si="20"/>
+        <v>0.8</v>
+      </c>
       <c r="AB82" s="1"/>
       <c r="AC82" s="1"/>
       <c r="AD82" s="1"/>
@@ -8754,7 +8989,7 @@
         <v>1</v>
       </c>
       <c r="L83" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M83" s="1"/>
@@ -8770,18 +9005,18 @@
         <v>0</v>
       </c>
       <c r="S83" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.2</v>
       </c>
       <c r="T83" s="5"/>
       <c r="U83" s="1">
-        <f t="shared" si="16"/>
-        <v>165</v>
-      </c>
-      <c r="V83" s="1">
         <f t="shared" si="17"/>
         <v>165</v>
       </c>
+      <c r="V83" s="1">
+        <f t="shared" si="18"/>
+        <v>165</v>
+      </c>
       <c r="W83" s="1">
         <v>0.4</v>
       </c>
@@ -8790,10 +9025,13 @@
       </c>
       <c r="Y83" s="1"/>
       <c r="Z83" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA83" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA83" s="1">
+        <f t="shared" si="20"/>
+        <v>6.9999999999999993E-2</v>
+      </c>
       <c r="AB83" s="1"/>
       <c r="AC83" s="1"/>
       <c r="AD83" s="1"/>
@@ -8848,7 +9086,7 @@
         <v>15</v>
       </c>
       <c r="L84" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-4</v>
       </c>
       <c r="M84" s="1"/>
@@ -8864,18 +9102,18 @@
         <v>0</v>
       </c>
       <c r="S84" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="T84" s="5"/>
       <c r="U84" s="1">
-        <f t="shared" si="16"/>
-        <v>16.932310114128295</v>
-      </c>
-      <c r="V84" s="1">
         <f t="shared" si="17"/>
         <v>16.932310114128295</v>
       </c>
+      <c r="V84" s="1">
+        <f t="shared" si="18"/>
+        <v>16.932310114128295</v>
+      </c>
       <c r="W84" s="1">
         <v>0</v>
       </c>
@@ -8884,10 +9122,13 @@
       </c>
       <c r="Y84" s="1"/>
       <c r="Z84" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA84" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA84" s="1">
+        <f t="shared" si="20"/>
+        <v>0.77</v>
+      </c>
       <c r="AB84" s="1"/>
       <c r="AC84" s="1"/>
       <c r="AD84" s="1"/>
@@ -8932,7 +9173,7 @@
       <c r="J85" s="10"/>
       <c r="K85" s="10"/>
       <c r="L85" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M85" s="10"/>
@@ -8946,18 +9187,18 @@
         <v>0</v>
       </c>
       <c r="S85" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="T85" s="12"/>
       <c r="U85" s="10" t="e">
-        <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V85" s="10" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="V85" s="10" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="W85" s="10">
         <v>0</v>
       </c>
@@ -8968,10 +9209,13 @@
         <v>34</v>
       </c>
       <c r="Z85" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA85" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA85" s="1">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
       <c r="AB85" s="1"/>
       <c r="AC85" s="1"/>
       <c r="AD85" s="1"/>
@@ -9016,7 +9260,7 @@
       <c r="J86" s="10"/>
       <c r="K86" s="10"/>
       <c r="L86" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M86" s="10"/>
@@ -9030,18 +9274,18 @@
         <v>0</v>
       </c>
       <c r="S86" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="T86" s="12"/>
       <c r="U86" s="10" t="e">
-        <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V86" s="10" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="V86" s="10" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="W86" s="10">
         <v>0</v>
       </c>
@@ -9052,10 +9296,13 @@
         <v>34</v>
       </c>
       <c r="Z86" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA86" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA86" s="1">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
       <c r="AB86" s="1"/>
       <c r="AC86" s="1"/>
       <c r="AD86" s="1"/>
@@ -9100,7 +9347,7 @@
       <c r="J87" s="10"/>
       <c r="K87" s="10"/>
       <c r="L87" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M87" s="10"/>
@@ -9114,18 +9361,18 @@
         <v>0</v>
       </c>
       <c r="S87" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="T87" s="12"/>
       <c r="U87" s="10" t="e">
-        <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V87" s="10" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="V87" s="10" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="W87" s="10">
         <v>0</v>
       </c>
@@ -9136,10 +9383,13 @@
         <v>34</v>
       </c>
       <c r="Z87" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA87" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA87" s="1">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
       <c r="AB87" s="1"/>
       <c r="AC87" s="1"/>
       <c r="AD87" s="1"/>
@@ -9196,7 +9446,7 @@
         <v>89.9</v>
       </c>
       <c r="L88" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-77.800000000000011</v>
       </c>
       <c r="M88" s="1"/>
@@ -9212,18 +9462,18 @@
         <v>0</v>
       </c>
       <c r="S88" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2.42</v>
       </c>
       <c r="T88" s="5"/>
       <c r="U88" s="1">
-        <f t="shared" si="16"/>
-        <v>111.78181818181818</v>
-      </c>
-      <c r="V88" s="1">
         <f t="shared" si="17"/>
         <v>111.78181818181818</v>
       </c>
+      <c r="V88" s="1">
+        <f t="shared" si="18"/>
+        <v>111.78181818181818</v>
+      </c>
       <c r="W88" s="1">
         <v>12.898199999999999</v>
       </c>
@@ -9232,10 +9482,13 @@
       </c>
       <c r="Y88" s="1"/>
       <c r="Z88" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA88" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA88" s="1">
+        <f t="shared" si="20"/>
+        <v>2.42</v>
+      </c>
       <c r="AB88" s="1"/>
       <c r="AC88" s="1"/>
       <c r="AD88" s="1"/>
@@ -9280,7 +9533,7 @@
       <c r="J89" s="10"/>
       <c r="K89" s="10"/>
       <c r="L89" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M89" s="10"/>
@@ -9294,18 +9547,18 @@
         <v>0</v>
       </c>
       <c r="S89" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="T89" s="12"/>
       <c r="U89" s="10" t="e">
-        <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V89" s="10" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="V89" s="10" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="W89" s="10">
         <v>0</v>
       </c>
@@ -9316,10 +9569,13 @@
         <v>34</v>
       </c>
       <c r="Z89" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA89" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA89" s="1">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
       <c r="AB89" s="1"/>
       <c r="AC89" s="1"/>
       <c r="AD89" s="1"/>
@@ -9376,7 +9632,7 @@
         <v>567.5</v>
       </c>
       <c r="L90" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-9.68100000000004</v>
       </c>
       <c r="M90" s="1"/>
@@ -9392,19 +9648,19 @@
         <v>0</v>
       </c>
       <c r="S90" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>111.56379999999999</v>
       </c>
       <c r="T90" s="5">
-        <f t="shared" ref="T90:T92" si="20">12*S90-R90-Q90-P90-O90-F90</f>
+        <f t="shared" ref="T90:T92" si="22">12*S90-R90-Q90-P90-O90-F90</f>
         <v>27.225830600724521</v>
       </c>
       <c r="U90" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>11.999999999999998</v>
       </c>
       <c r="V90" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>11.755961785088671</v>
       </c>
       <c r="W90" s="1">
@@ -9415,10 +9671,13 @@
       </c>
       <c r="Y90" s="1"/>
       <c r="Z90" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>27</v>
       </c>
-      <c r="AA90" s="1"/>
+      <c r="AA90" s="1">
+        <f t="shared" si="20"/>
+        <v>111.56379999999999</v>
+      </c>
       <c r="AB90" s="1"/>
       <c r="AC90" s="1"/>
       <c r="AD90" s="1"/>
@@ -9475,7 +9734,7 @@
         <v>598.5</v>
       </c>
       <c r="L91" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-103.83800000000002</v>
       </c>
       <c r="M91" s="1"/>
@@ -9491,19 +9750,19 @@
         <v>0</v>
       </c>
       <c r="S91" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>98.932400000000001</v>
       </c>
       <c r="T91" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>479.92177665822271</v>
       </c>
       <c r="U91" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>11.999999999999998</v>
       </c>
       <c r="V91" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>7.1489928814198098</v>
       </c>
       <c r="W91" s="1">
@@ -9514,10 +9773,13 @@
       </c>
       <c r="Y91" s="1"/>
       <c r="Z91" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>480</v>
       </c>
-      <c r="AA91" s="1"/>
+      <c r="AA91" s="1">
+        <f t="shared" si="20"/>
+        <v>98.932400000000001</v>
+      </c>
       <c r="AB91" s="1"/>
       <c r="AC91" s="1"/>
       <c r="AD91" s="1"/>
@@ -9576,7 +9838,7 @@
         <v>759</v>
       </c>
       <c r="L92" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-78.182999999999993</v>
       </c>
       <c r="M92" s="1"/>
@@ -9592,19 +9854,19 @@
         <v>251.10125231080929</v>
       </c>
       <c r="S92" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>136.1634</v>
       </c>
       <c r="T92" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>234.9879999999996</v>
       </c>
       <c r="U92" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>12</v>
       </c>
       <c r="V92" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>10.274220532095999</v>
       </c>
       <c r="W92" s="1">
@@ -9615,10 +9877,13 @@
       </c>
       <c r="Y92" s="1"/>
       <c r="Z92" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>235</v>
       </c>
-      <c r="AA92" s="1"/>
+      <c r="AA92" s="1">
+        <f t="shared" si="20"/>
+        <v>136.1634</v>
+      </c>
       <c r="AB92" s="1"/>
       <c r="AC92" s="1"/>
       <c r="AD92" s="1"/>
@@ -9663,7 +9928,7 @@
       <c r="J93" s="10"/>
       <c r="K93" s="10"/>
       <c r="L93" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M93" s="10"/>
@@ -9677,18 +9942,18 @@
         <v>0</v>
       </c>
       <c r="S93" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="T93" s="12"/>
       <c r="U93" s="10" t="e">
-        <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V93" s="10" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="V93" s="10" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="W93" s="10">
         <v>0</v>
       </c>
@@ -9699,10 +9964,13 @@
         <v>34</v>
       </c>
       <c r="Z93" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA93" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA93" s="1">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
       <c r="AB93" s="1"/>
       <c r="AC93" s="1"/>
       <c r="AD93" s="1"/>
@@ -9751,7 +10019,7 @@
         <v>6</v>
       </c>
       <c r="L94" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-6</v>
       </c>
       <c r="M94" s="1"/>
@@ -9767,18 +10035,18 @@
         <v>100</v>
       </c>
       <c r="S94" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="T94" s="5"/>
       <c r="U94" s="1" t="e">
-        <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V94" s="1" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="V94" s="1" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="W94" s="1">
         <v>0</v>
       </c>
@@ -9787,10 +10055,13 @@
       </c>
       <c r="Y94" s="1"/>
       <c r="Z94" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA94" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA94" s="1">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
       <c r="AB94" s="1"/>
       <c r="AC94" s="1"/>
       <c r="AD94" s="1"/>
@@ -9835,7 +10106,7 @@
       <c r="J95" s="10"/>
       <c r="K95" s="10"/>
       <c r="L95" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M95" s="10"/>
@@ -9849,18 +10120,18 @@
         <v>0</v>
       </c>
       <c r="S95" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="T95" s="12"/>
       <c r="U95" s="10" t="e">
-        <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V95" s="10" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="V95" s="10" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="W95" s="10">
         <v>0</v>
       </c>
@@ -9871,10 +10142,13 @@
         <v>34</v>
       </c>
       <c r="Z95" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA95" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA95" s="1">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
       <c r="AB95" s="1"/>
       <c r="AC95" s="1"/>
       <c r="AD95" s="1"/>
@@ -9929,7 +10203,7 @@
         <v>11</v>
       </c>
       <c r="L96" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-1</v>
       </c>
       <c r="M96" s="1"/>
@@ -9945,18 +10219,18 @@
         <v>50</v>
       </c>
       <c r="S96" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2</v>
       </c>
       <c r="T96" s="5"/>
       <c r="U96" s="1">
-        <f t="shared" si="16"/>
-        <v>35.671875</v>
-      </c>
-      <c r="V96" s="1">
         <f t="shared" si="17"/>
         <v>35.671875</v>
       </c>
+      <c r="V96" s="1">
+        <f t="shared" si="18"/>
+        <v>35.671875</v>
+      </c>
       <c r="W96" s="1">
         <v>0.6</v>
       </c>
@@ -9965,10 +10239,13 @@
       </c>
       <c r="Y96" s="1"/>
       <c r="Z96" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA96" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA96" s="1">
+        <f t="shared" si="20"/>
+        <v>0.14000000000000001</v>
+      </c>
       <c r="AB96" s="1"/>
       <c r="AC96" s="1"/>
       <c r="AD96" s="1"/>
@@ -10021,7 +10298,7 @@
         <v>9</v>
       </c>
       <c r="L97" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-6</v>
       </c>
       <c r="M97" s="1"/>
@@ -10039,18 +10316,18 @@
         <v>40</v>
       </c>
       <c r="S97" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.6</v>
       </c>
       <c r="T97" s="5">
         <v>10</v>
       </c>
       <c r="U97" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>111.65559246954597</v>
       </c>
       <c r="V97" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>94.988925802879294</v>
       </c>
       <c r="W97" s="1">
@@ -10061,10 +10338,13 @@
       </c>
       <c r="Y97" s="1"/>
       <c r="Z97" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="AA97" s="1"/>
+      <c r="AA97" s="1">
+        <f t="shared" si="20"/>
+        <v>4.2000000000000003E-2</v>
+      </c>
       <c r="AB97" s="1"/>
       <c r="AC97" s="1"/>
       <c r="AD97" s="1"/>
@@ -10119,7 +10399,7 @@
         <v>31</v>
       </c>
       <c r="L98" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-12</v>
       </c>
       <c r="M98" s="1"/>
@@ -10135,18 +10415,18 @@
         <v>0</v>
       </c>
       <c r="S98" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>3.8</v>
       </c>
       <c r="T98" s="5">
         <v>10</v>
       </c>
       <c r="U98" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>19.54765947125879</v>
       </c>
       <c r="V98" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>16.916080523890368</v>
       </c>
       <c r="W98" s="1">
@@ -10157,10 +10437,13 @@
       </c>
       <c r="Y98" s="1"/>
       <c r="Z98" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="AA98" s="1"/>
+      <c r="AA98" s="1">
+        <f t="shared" si="20"/>
+        <v>0.26600000000000001</v>
+      </c>
       <c r="AB98" s="1"/>
       <c r="AC98" s="1"/>
       <c r="AD98" s="1"/>
@@ -10215,7 +10498,7 @@
         <v>35</v>
       </c>
       <c r="L99" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-5</v>
       </c>
       <c r="M99" s="1"/>
@@ -10231,19 +10514,19 @@
         <v>20</v>
       </c>
       <c r="S99" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>6</v>
       </c>
       <c r="T99" s="5">
-        <f t="shared" ref="T99:T100" si="21">12*S99-R99-Q99-P99-O99-F99</f>
+        <f t="shared" ref="T99:T100" si="23">12*S99-R99-Q99-P99-O99-F99</f>
         <v>20</v>
       </c>
       <c r="U99" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>12</v>
       </c>
       <c r="V99" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>8.6666666666666661</v>
       </c>
       <c r="W99" s="1">
@@ -10254,10 +10537,13 @@
       </c>
       <c r="Y99" s="1"/>
       <c r="Z99" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>6</v>
       </c>
-      <c r="AA99" s="1"/>
+      <c r="AA99" s="1">
+        <f t="shared" si="20"/>
+        <v>1.7999999999999998</v>
+      </c>
       <c r="AB99" s="1"/>
       <c r="AC99" s="1"/>
       <c r="AD99" s="1"/>
@@ -10314,7 +10600,7 @@
         <v>21.9</v>
       </c>
       <c r="L100" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-5.3719999999999999</v>
       </c>
       <c r="M100" s="1"/>
@@ -10330,19 +10616,19 @@
         <v>0</v>
       </c>
       <c r="S100" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>3.3055999999999996</v>
       </c>
       <c r="T100" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>20.954199999999993</v>
       </c>
       <c r="U100" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>12</v>
       </c>
       <c r="V100" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>5.660999515972895</v>
       </c>
       <c r="W100" s="1">
@@ -10353,10 +10639,13 @@
       </c>
       <c r="Y100" s="1"/>
       <c r="Z100" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>21</v>
       </c>
-      <c r="AA100" s="1"/>
+      <c r="AA100" s="1">
+        <f t="shared" si="20"/>
+        <v>3.3055999999999996</v>
+      </c>
       <c r="AB100" s="1"/>
       <c r="AC100" s="1"/>
       <c r="AD100" s="1"/>
@@ -10411,7 +10700,7 @@
         <v>42</v>
       </c>
       <c r="L101" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-22</v>
       </c>
       <c r="M101" s="1"/>
@@ -10427,18 +10716,18 @@
         <v>0</v>
       </c>
       <c r="S101" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>4</v>
       </c>
       <c r="T101" s="5"/>
       <c r="U101" s="1">
-        <f t="shared" si="16"/>
-        <v>18.75</v>
-      </c>
-      <c r="V101" s="1">
         <f t="shared" si="17"/>
         <v>18.75</v>
       </c>
+      <c r="V101" s="1">
+        <f t="shared" si="18"/>
+        <v>18.75</v>
+      </c>
       <c r="W101" s="1">
         <v>2</v>
       </c>
@@ -10449,10 +10738,13 @@
         <v>61</v>
       </c>
       <c r="Z101" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA101" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA101" s="1">
+        <f t="shared" si="20"/>
+        <v>0.44</v>
+      </c>
       <c r="AB101" s="1"/>
       <c r="AC101" s="1"/>
       <c r="AD101" s="1"/>
@@ -10497,7 +10789,7 @@
       <c r="J102" s="10"/>
       <c r="K102" s="10"/>
       <c r="L102" s="10">
-        <f t="shared" ref="L102:L131" si="22">E102-K102</f>
+        <f t="shared" ref="L102:L131" si="24">E102-K102</f>
         <v>0</v>
       </c>
       <c r="M102" s="10"/>
@@ -10511,16 +10803,16 @@
         <v>0</v>
       </c>
       <c r="S102" s="10">
-        <f t="shared" ref="S102:S131" si="23">E102/5</f>
+        <f t="shared" ref="S102:S131" si="25">E102/5</f>
         <v>0</v>
       </c>
       <c r="T102" s="12"/>
       <c r="U102" s="10" t="e">
-        <f t="shared" ref="U102:U131" si="24">(F102+O102+P102+Q102+R102+T102)/S102</f>
+        <f t="shared" ref="U102:U131" si="26">(F102+O102+P102+Q102+R102+T102)/S102</f>
         <v>#DIV/0!</v>
       </c>
       <c r="V102" s="10" t="e">
-        <f t="shared" ref="V102:V131" si="25">(F102+O102+P102+Q102+R102)/S102</f>
+        <f t="shared" ref="V102:V131" si="27">(F102+O102+P102+Q102+R102)/S102</f>
         <v>#DIV/0!</v>
       </c>
       <c r="W102" s="10">
@@ -10533,10 +10825,13 @@
         <v>166</v>
       </c>
       <c r="Z102" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA102" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA102" s="1">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
       <c r="AB102" s="1"/>
       <c r="AC102" s="1"/>
       <c r="AD102" s="1"/>
@@ -10585,7 +10880,7 @@
         <v>9</v>
       </c>
       <c r="L103" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-9</v>
       </c>
       <c r="M103" s="1"/>
@@ -10601,16 +10896,16 @@
         <v>30</v>
       </c>
       <c r="S103" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="T103" s="5"/>
       <c r="U103" s="1" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V103" s="1" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W103" s="1">
@@ -10621,10 +10916,13 @@
       </c>
       <c r="Y103" s="1"/>
       <c r="Z103" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA103" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA103" s="1">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
       <c r="AB103" s="1"/>
       <c r="AC103" s="1"/>
       <c r="AD103" s="1"/>
@@ -10681,7 +10979,7 @@
         <v>34</v>
       </c>
       <c r="L104" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="M104" s="1"/>
@@ -10697,19 +10995,19 @@
         <v>0</v>
       </c>
       <c r="S104" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>6.8</v>
       </c>
       <c r="T104" s="5">
-        <f t="shared" ref="T104" si="26">12*S104-R104-Q104-P104-O104-F104</f>
+        <f t="shared" ref="T104" si="28">12*S104-R104-Q104-P104-O104-F104</f>
         <v>5.7756838905775041</v>
       </c>
       <c r="U104" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>12</v>
       </c>
       <c r="V104" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>11.150634721973894</v>
       </c>
       <c r="W104" s="1">
@@ -10720,10 +11018,13 @@
       </c>
       <c r="Y104" s="1"/>
       <c r="Z104" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA104" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA104" s="1">
+        <f t="shared" si="20"/>
+        <v>0.54400000000000004</v>
+      </c>
       <c r="AB104" s="1"/>
       <c r="AC104" s="1"/>
       <c r="AD104" s="1"/>
@@ -10770,7 +11071,7 @@
       <c r="J105" s="1"/>
       <c r="K105" s="1"/>
       <c r="L105" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="M105" s="1"/>
@@ -10786,16 +11087,16 @@
         <v>0</v>
       </c>
       <c r="S105" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="T105" s="5"/>
       <c r="U105" s="1" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V105" s="1" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W105" s="1">
@@ -10806,10 +11107,13 @@
       </c>
       <c r="Y105" s="1"/>
       <c r="Z105" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA105" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA105" s="1">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
       <c r="AB105" s="1"/>
       <c r="AC105" s="1"/>
       <c r="AD105" s="1"/>
@@ -10858,7 +11162,7 @@
         <v>17.899999999999999</v>
       </c>
       <c r="L106" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-17.899999999999999</v>
       </c>
       <c r="M106" s="1"/>
@@ -10874,16 +11178,16 @@
         <v>200</v>
       </c>
       <c r="S106" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="T106" s="5"/>
       <c r="U106" s="1" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V106" s="1" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W106" s="1">
@@ -10894,10 +11198,13 @@
       </c>
       <c r="Y106" s="1"/>
       <c r="Z106" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA106" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA106" s="1">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
       <c r="AB106" s="1"/>
       <c r="AC106" s="1"/>
       <c r="AD106" s="1"/>
@@ -10952,7 +11259,7 @@
         <v>44.4</v>
       </c>
       <c r="L107" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-4.7959999999999994</v>
       </c>
       <c r="M107" s="1"/>
@@ -10970,16 +11277,16 @@
         <v>0</v>
       </c>
       <c r="S107" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>7.9207999999999998</v>
       </c>
       <c r="T107" s="5"/>
       <c r="U107" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>25.197203951773218</v>
       </c>
       <c r="V107" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>25.197203951773218</v>
       </c>
       <c r="W107" s="1">
@@ -10990,10 +11297,13 @@
       </c>
       <c r="Y107" s="1"/>
       <c r="Z107" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA107" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA107" s="1">
+        <f t="shared" si="20"/>
+        <v>7.9207999999999998</v>
+      </c>
       <c r="AB107" s="1"/>
       <c r="AC107" s="1"/>
       <c r="AD107" s="1"/>
@@ -11042,7 +11352,7 @@
         <v>1.5</v>
       </c>
       <c r="L108" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-1.5</v>
       </c>
       <c r="M108" s="1"/>
@@ -11060,16 +11370,16 @@
         <v>200</v>
       </c>
       <c r="S108" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="T108" s="5"/>
       <c r="U108" s="1" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V108" s="1" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W108" s="1">
@@ -11080,10 +11390,13 @@
       </c>
       <c r="Y108" s="1"/>
       <c r="Z108" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA108" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA108" s="1">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
       <c r="AB108" s="1"/>
       <c r="AC108" s="1"/>
       <c r="AD108" s="1"/>
@@ -11128,7 +11441,7 @@
       <c r="J109" s="10"/>
       <c r="K109" s="10"/>
       <c r="L109" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="M109" s="10"/>
@@ -11142,16 +11455,16 @@
         <v>0</v>
       </c>
       <c r="S109" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="T109" s="12"/>
       <c r="U109" s="10" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V109" s="10" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W109" s="10">
@@ -11164,10 +11477,13 @@
         <v>34</v>
       </c>
       <c r="Z109" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA109" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA109" s="1">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
       <c r="AB109" s="1"/>
       <c r="AC109" s="1"/>
       <c r="AD109" s="1"/>
@@ -11212,7 +11528,7 @@
       <c r="J110" s="10"/>
       <c r="K110" s="10"/>
       <c r="L110" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="M110" s="10"/>
@@ -11226,16 +11542,16 @@
         <v>0</v>
       </c>
       <c r="S110" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="T110" s="12"/>
       <c r="U110" s="10" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V110" s="10" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W110" s="10">
@@ -11248,10 +11564,13 @@
         <v>34</v>
       </c>
       <c r="Z110" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA110" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA110" s="1">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
       <c r="AB110" s="1"/>
       <c r="AC110" s="1"/>
       <c r="AD110" s="1"/>
@@ -11300,7 +11619,7 @@
         <v>2</v>
       </c>
       <c r="L111" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-2</v>
       </c>
       <c r="M111" s="1"/>
@@ -11316,16 +11635,16 @@
         <v>150</v>
       </c>
       <c r="S111" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="T111" s="5"/>
       <c r="U111" s="1" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V111" s="1" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W111" s="1">
@@ -11336,10 +11655,13 @@
       </c>
       <c r="Y111" s="1"/>
       <c r="Z111" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA111" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA111" s="1">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
       <c r="AB111" s="1"/>
       <c r="AC111" s="1"/>
       <c r="AD111" s="1"/>
@@ -11394,7 +11716,7 @@
         <v>83</v>
       </c>
       <c r="L112" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-7</v>
       </c>
       <c r="M112" s="1"/>
@@ -11410,16 +11732,16 @@
         <v>0</v>
       </c>
       <c r="S112" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>15.2</v>
       </c>
       <c r="T112" s="5"/>
       <c r="U112" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>14.736842105263159</v>
       </c>
       <c r="V112" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>14.736842105263159</v>
       </c>
       <c r="W112" s="1">
@@ -11430,10 +11752,13 @@
       </c>
       <c r="Y112" s="1"/>
       <c r="Z112" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA112" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA112" s="1">
+        <f t="shared" si="20"/>
+        <v>4.2560000000000002</v>
+      </c>
       <c r="AB112" s="1"/>
       <c r="AC112" s="1"/>
       <c r="AD112" s="1"/>
@@ -11482,7 +11807,7 @@
         <v>8</v>
       </c>
       <c r="L113" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-8</v>
       </c>
       <c r="M113" s="1"/>
@@ -11500,16 +11825,16 @@
         <v>150</v>
       </c>
       <c r="S113" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="T113" s="5"/>
       <c r="U113" s="1" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V113" s="1" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W113" s="1">
@@ -11520,10 +11845,13 @@
       </c>
       <c r="Y113" s="1"/>
       <c r="Z113" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA113" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA113" s="1">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
       <c r="AB113" s="1"/>
       <c r="AC113" s="1"/>
       <c r="AD113" s="1"/>
@@ -11578,7 +11906,7 @@
         <v>15</v>
       </c>
       <c r="L114" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="M114" s="1"/>
@@ -11594,19 +11922,19 @@
         <v>0</v>
       </c>
       <c r="S114" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>3</v>
       </c>
       <c r="T114" s="5">
-        <f t="shared" ref="T114:T130" si="27">12*S114-R114-Q114-P114-O114-F114</f>
+        <f t="shared" ref="T114:T130" si="29">12*S114-R114-Q114-P114-O114-F114</f>
         <v>17.033472803347284</v>
       </c>
       <c r="U114" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>12</v>
       </c>
       <c r="V114" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>6.3221757322175725</v>
       </c>
       <c r="W114" s="1">
@@ -11617,10 +11945,13 @@
       </c>
       <c r="Y114" s="1"/>
       <c r="Z114" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>2</v>
       </c>
-      <c r="AA114" s="1"/>
+      <c r="AA114" s="1">
+        <f t="shared" si="20"/>
+        <v>0.27</v>
+      </c>
       <c r="AB114" s="1"/>
       <c r="AC114" s="1"/>
       <c r="AD114" s="1"/>
@@ -11675,7 +12006,7 @@
         <v>25</v>
       </c>
       <c r="L115" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-10</v>
       </c>
       <c r="M115" s="1"/>
@@ -11691,19 +12022,19 @@
         <v>0</v>
       </c>
       <c r="S115" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>3</v>
       </c>
       <c r="T115" s="5">
+        <f t="shared" si="29"/>
+        <v>20.856000000000002</v>
+      </c>
+      <c r="U115" s="1">
+        <f t="shared" si="26"/>
+        <v>12</v>
+      </c>
+      <c r="V115" s="1">
         <f t="shared" si="27"/>
-        <v>20.856000000000002</v>
-      </c>
-      <c r="U115" s="1">
-        <f t="shared" si="24"/>
-        <v>12</v>
-      </c>
-      <c r="V115" s="1">
-        <f t="shared" si="25"/>
         <v>5.048</v>
       </c>
       <c r="W115" s="1">
@@ -11714,10 +12045,13 @@
       </c>
       <c r="Y115" s="1"/>
       <c r="Z115" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>21</v>
       </c>
-      <c r="AA115" s="1"/>
+      <c r="AA115" s="1">
+        <f t="shared" si="20"/>
+        <v>3</v>
+      </c>
       <c r="AB115" s="1"/>
       <c r="AC115" s="1"/>
       <c r="AD115" s="1"/>
@@ -11772,7 +12106,7 @@
         <v>12.5</v>
       </c>
       <c r="L116" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>9.0000000000003411E-3</v>
       </c>
       <c r="M116" s="1"/>
@@ -11788,16 +12122,16 @@
         <v>0</v>
       </c>
       <c r="S116" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>2.5018000000000002</v>
       </c>
       <c r="T116" s="5"/>
       <c r="U116" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>18.926772723638976</v>
       </c>
       <c r="V116" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>18.926772723638976</v>
       </c>
       <c r="W116" s="1">
@@ -11808,10 +12142,13 @@
       </c>
       <c r="Y116" s="1"/>
       <c r="Z116" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA116" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA116" s="1">
+        <f t="shared" si="20"/>
+        <v>2.5018000000000002</v>
+      </c>
       <c r="AB116" s="1"/>
       <c r="AC116" s="1"/>
       <c r="AD116" s="1"/>
@@ -11864,7 +12201,7 @@
         <v>34</v>
       </c>
       <c r="L117" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-25</v>
       </c>
       <c r="M117" s="1"/>
@@ -11880,18 +12217,18 @@
         <v>0</v>
       </c>
       <c r="S117" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1.8</v>
       </c>
       <c r="T117" s="5">
         <v>10</v>
       </c>
       <c r="U117" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>36.333333333333336</v>
       </c>
       <c r="V117" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>30.777777777777779</v>
       </c>
       <c r="W117" s="1">
@@ -11902,10 +12239,13 @@
       </c>
       <c r="Y117" s="1"/>
       <c r="Z117" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="AA117" s="1"/>
+      <c r="AA117" s="1">
+        <f t="shared" si="20"/>
+        <v>0.16200000000000001</v>
+      </c>
       <c r="AB117" s="1"/>
       <c r="AC117" s="1"/>
       <c r="AD117" s="1"/>
@@ -11960,7 +12300,7 @@
         <v>14</v>
       </c>
       <c r="L118" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="M118" s="1"/>
@@ -11976,19 +12316,19 @@
         <v>0</v>
       </c>
       <c r="S118" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>2.8</v>
       </c>
       <c r="T118" s="5">
+        <f t="shared" si="29"/>
+        <v>13.068292682926824</v>
+      </c>
+      <c r="U118" s="1">
+        <f t="shared" si="26"/>
+        <v>11.999999999999998</v>
+      </c>
+      <c r="V118" s="1">
         <f t="shared" si="27"/>
-        <v>13.068292682926824</v>
-      </c>
-      <c r="U118" s="1">
-        <f t="shared" si="24"/>
-        <v>11.999999999999998</v>
-      </c>
-      <c r="V118" s="1">
-        <f t="shared" si="25"/>
         <v>7.3327526132404186</v>
       </c>
       <c r="W118" s="1">
@@ -11999,10 +12339,13 @@
       </c>
       <c r="Y118" s="1"/>
       <c r="Z118" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="AA118" s="1"/>
+      <c r="AA118" s="1">
+        <f t="shared" si="20"/>
+        <v>0.252</v>
+      </c>
       <c r="AB118" s="1"/>
       <c r="AC118" s="1"/>
       <c r="AD118" s="1"/>
@@ -12057,7 +12400,7 @@
         <v>10.1</v>
       </c>
       <c r="L119" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0.87800000000000011</v>
       </c>
       <c r="M119" s="1"/>
@@ -12073,16 +12416,16 @@
         <v>50</v>
       </c>
       <c r="S119" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>2.1955999999999998</v>
       </c>
       <c r="T119" s="5"/>
       <c r="U119" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>39.094747014114979</v>
       </c>
       <c r="V119" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>39.094747014114979</v>
       </c>
       <c r="W119" s="1">
@@ -12093,10 +12436,13 @@
       </c>
       <c r="Y119" s="1"/>
       <c r="Z119" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA119" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA119" s="1">
+        <f t="shared" si="20"/>
+        <v>2.1955999999999998</v>
+      </c>
       <c r="AB119" s="1"/>
       <c r="AC119" s="1"/>
       <c r="AD119" s="1"/>
@@ -12153,7 +12499,7 @@
         <v>74.400000000000006</v>
       </c>
       <c r="L120" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-12.495000000000005</v>
       </c>
       <c r="M120" s="1"/>
@@ -12169,16 +12515,16 @@
         <v>70</v>
       </c>
       <c r="S120" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>12.381</v>
       </c>
       <c r="T120" s="5"/>
       <c r="U120" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>17.2414183022373</v>
       </c>
       <c r="V120" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>17.2414183022373</v>
       </c>
       <c r="W120" s="1">
@@ -12189,10 +12535,13 @@
       </c>
       <c r="Y120" s="1"/>
       <c r="Z120" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA120" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA120" s="1">
+        <f t="shared" si="20"/>
+        <v>12.381</v>
+      </c>
       <c r="AB120" s="1"/>
       <c r="AC120" s="1"/>
       <c r="AD120" s="1"/>
@@ -12249,7 +12598,7 @@
         <v>9.5</v>
       </c>
       <c r="L121" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-2.806</v>
       </c>
       <c r="M121" s="1"/>
@@ -12265,16 +12614,16 @@
         <v>0</v>
       </c>
       <c r="S121" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1.3388</v>
       </c>
       <c r="T121" s="5"/>
       <c r="U121" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>16.540035853002692</v>
       </c>
       <c r="V121" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>16.540035853002692</v>
       </c>
       <c r="W121" s="1">
@@ -12285,10 +12634,13 @@
       </c>
       <c r="Y121" s="1"/>
       <c r="Z121" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA121" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA121" s="1">
+        <f t="shared" si="20"/>
+        <v>1.3388</v>
+      </c>
       <c r="AB121" s="1"/>
       <c r="AC121" s="1"/>
       <c r="AD121" s="1"/>
@@ -12347,7 +12699,7 @@
         <v>415</v>
       </c>
       <c r="L122" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-62.491999999999962</v>
       </c>
       <c r="M122" s="1"/>
@@ -12363,16 +12715,16 @@
         <v>187.0712</v>
       </c>
       <c r="S122" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>70.50160000000001</v>
       </c>
       <c r="T122" s="5"/>
       <c r="U122" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>19.058761786966535</v>
       </c>
       <c r="V122" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>19.058761786966535</v>
       </c>
       <c r="W122" s="1">
@@ -12383,10 +12735,13 @@
       </c>
       <c r="Y122" s="1"/>
       <c r="Z122" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA122" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA122" s="1">
+        <f t="shared" si="20"/>
+        <v>70.50160000000001</v>
+      </c>
       <c r="AB122" s="1"/>
       <c r="AC122" s="1"/>
       <c r="AD122" s="1"/>
@@ -12441,7 +12796,7 @@
         <v>15</v>
       </c>
       <c r="L123" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="M123" s="1"/>
@@ -12457,16 +12812,16 @@
         <v>0</v>
       </c>
       <c r="S123" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>3</v>
       </c>
       <c r="T123" s="5"/>
       <c r="U123" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>86</v>
       </c>
       <c r="V123" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>86</v>
       </c>
       <c r="W123" s="1">
@@ -12479,10 +12834,13 @@
         <v>50</v>
       </c>
       <c r="Z123" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA123" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA123" s="1">
+        <f t="shared" si="20"/>
+        <v>0.75</v>
+      </c>
       <c r="AB123" s="1"/>
       <c r="AC123" s="1"/>
       <c r="AD123" s="1"/>
@@ -12539,7 +12897,7 @@
         <v>21</v>
       </c>
       <c r="L124" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-5</v>
       </c>
       <c r="M124" s="1"/>
@@ -12555,16 +12913,16 @@
         <v>0</v>
       </c>
       <c r="S124" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>3.2</v>
       </c>
       <c r="T124" s="5"/>
       <c r="U124" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>33.75</v>
       </c>
       <c r="V124" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>33.75</v>
       </c>
       <c r="W124" s="1">
@@ -12577,10 +12935,13 @@
         <v>50</v>
       </c>
       <c r="Z124" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA124" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA124" s="1">
+        <f t="shared" si="20"/>
+        <v>1.04</v>
+      </c>
       <c r="AB124" s="1"/>
       <c r="AC124" s="1"/>
       <c r="AD124" s="1"/>
@@ -12637,7 +12998,7 @@
         <v>26</v>
       </c>
       <c r="L125" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-5</v>
       </c>
       <c r="M125" s="1"/>
@@ -12653,16 +13014,16 @@
         <v>0</v>
       </c>
       <c r="S125" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>4.2</v>
       </c>
       <c r="T125" s="5"/>
       <c r="U125" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>25.714285714285712</v>
       </c>
       <c r="V125" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>25.714285714285712</v>
       </c>
       <c r="W125" s="1">
@@ -12675,10 +13036,13 @@
         <v>50</v>
       </c>
       <c r="Z125" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA125" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA125" s="1">
+        <f t="shared" si="20"/>
+        <v>1.05</v>
+      </c>
       <c r="AB125" s="1"/>
       <c r="AC125" s="1"/>
       <c r="AD125" s="1"/>
@@ -12727,7 +13091,7 @@
         <v>7</v>
       </c>
       <c r="L126" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-7</v>
       </c>
       <c r="M126" s="1"/>
@@ -12745,16 +13109,16 @@
         <v>80</v>
       </c>
       <c r="S126" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="T126" s="5"/>
       <c r="U126" s="1" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V126" s="1" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W126" s="1">
@@ -12765,10 +13129,13 @@
       </c>
       <c r="Y126" s="1"/>
       <c r="Z126" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA126" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA126" s="1">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
       <c r="AB126" s="1"/>
       <c r="AC126" s="1"/>
       <c r="AD126" s="1"/>
@@ -12817,7 +13184,7 @@
         <v>7</v>
       </c>
       <c r="L127" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-7</v>
       </c>
       <c r="M127" s="1"/>
@@ -12835,16 +13202,16 @@
         <v>80</v>
       </c>
       <c r="S127" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="T127" s="5"/>
       <c r="U127" s="1" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V127" s="1" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W127" s="1">
@@ -12855,10 +13222,13 @@
       </c>
       <c r="Y127" s="1"/>
       <c r="Z127" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA127" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA127" s="1">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
       <c r="AB127" s="1"/>
       <c r="AC127" s="1"/>
       <c r="AD127" s="1"/>
@@ -12907,7 +13277,7 @@
         <v>7.5</v>
       </c>
       <c r="L128" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-7.5</v>
       </c>
       <c r="M128" s="1"/>
@@ -12923,16 +13293,16 @@
         <v>0</v>
       </c>
       <c r="S128" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="T128" s="5"/>
       <c r="U128" s="1" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V128" s="1" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W128" s="1">
@@ -12943,10 +13313,13 @@
       </c>
       <c r="Y128" s="1"/>
       <c r="Z128" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA128" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA128" s="1">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
       <c r="AB128" s="1"/>
       <c r="AC128" s="1"/>
       <c r="AD128" s="1"/>
@@ -12995,7 +13368,7 @@
         <v>1</v>
       </c>
       <c r="L129" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-1</v>
       </c>
       <c r="M129" s="1"/>
@@ -13013,16 +13386,16 @@
         <v>80</v>
       </c>
       <c r="S129" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="T129" s="5"/>
       <c r="U129" s="1" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V129" s="1" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W129" s="1">
@@ -13033,10 +13406,13 @@
       </c>
       <c r="Y129" s="1"/>
       <c r="Z129" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA129" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA129" s="1">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
       <c r="AB129" s="1"/>
       <c r="AC129" s="1"/>
       <c r="AD129" s="1"/>
@@ -13091,7 +13467,7 @@
         <v>20</v>
       </c>
       <c r="L130" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-5</v>
       </c>
       <c r="M130" s="1"/>
@@ -13107,19 +13483,19 @@
         <v>0</v>
       </c>
       <c r="S130" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>3</v>
       </c>
       <c r="T130" s="5">
+        <f t="shared" si="29"/>
+        <v>9.3333333333333286</v>
+      </c>
+      <c r="U130" s="1">
+        <f t="shared" si="26"/>
+        <v>12</v>
+      </c>
+      <c r="V130" s="1">
         <f t="shared" si="27"/>
-        <v>9.3333333333333286</v>
-      </c>
-      <c r="U130" s="1">
-        <f t="shared" si="24"/>
-        <v>12</v>
-      </c>
-      <c r="V130" s="1">
-        <f t="shared" si="25"/>
         <v>8.8888888888888911</v>
       </c>
       <c r="W130" s="1">
@@ -13130,10 +13506,13 @@
       </c>
       <c r="Y130" s="1"/>
       <c r="Z130" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="AA130" s="1"/>
+      <c r="AA130" s="1">
+        <f t="shared" si="20"/>
+        <v>0.36</v>
+      </c>
       <c r="AB130" s="1"/>
       <c r="AC130" s="1"/>
       <c r="AD130" s="1"/>
@@ -13190,7 +13569,7 @@
         <v>24</v>
       </c>
       <c r="L131" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-1</v>
       </c>
       <c r="M131" s="10"/>
@@ -13204,16 +13583,16 @@
         <v>0</v>
       </c>
       <c r="S131" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>4.5999999999999996</v>
       </c>
       <c r="T131" s="12"/>
       <c r="U131" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>-8.0434782608695663</v>
       </c>
       <c r="V131" s="10">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-8.0434782608695663</v>
       </c>
       <c r="W131" s="10">
@@ -13224,10 +13603,13 @@
       </c>
       <c r="Y131" s="10"/>
       <c r="Z131" s="1">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AA131" s="1"/>
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AA131" s="1">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
       <c r="AB131" s="1"/>
       <c r="AC131" s="1"/>
       <c r="AD131" s="1"/>
